--- a/Out_put/OilAnalysis_Results_v5.xlsx
+++ b/Out_put/OilAnalysis_Results_v5.xlsx
@@ -8881,7 +8881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sMAPE(%)</t>
+          <t>MASE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -8932,7 +8932,7 @@
         <v>0.297974</v>
       </c>
       <c r="E2" t="n">
-        <v>195.696124</v>
+        <v>0.5856749999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.721931</v>
@@ -8941,95 +8941,95 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>GARCH-t</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.065065</v>
+        <v>0.061965</v>
       </c>
       <c r="C3" t="n">
-        <v>0.080884</v>
+        <v>0.079566</v>
       </c>
       <c r="D3" t="n">
-        <v>0.309942</v>
+        <v>0.299928</v>
       </c>
       <c r="E3" t="n">
-        <v>171.127489</v>
+        <v>0.570679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.736286</v>
+        <v>0.724294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GARCH(1,1)</t>
+          <t>SARIMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.062705</v>
+        <v>0.065065</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08096200000000001</v>
+        <v>0.080884</v>
       </c>
       <c r="D4" t="n">
-        <v>0.310539</v>
+        <v>0.309942</v>
       </c>
       <c r="E4" t="n">
-        <v>132.454442</v>
+        <v>0.599224</v>
       </c>
       <c r="F4" t="n">
-        <v>0.736994</v>
+        <v>0.736286</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ARCH(1)</t>
+          <t>GARCH(1,1)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.062777</v>
+        <v>0.062705</v>
       </c>
       <c r="C5" t="n">
-        <v>0.081053</v>
+        <v>0.08096200000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.311243</v>
+        <v>0.310539</v>
       </c>
       <c r="E5" t="n">
-        <v>132.131178</v>
+        <v>0.577494</v>
       </c>
       <c r="F5" t="n">
-        <v>0.73783</v>
+        <v>0.736994</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OLS</t>
+          <t>ARCH(1)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.073737</v>
+        <v>0.062777</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09384199999999999</v>
+        <v>0.081053</v>
       </c>
       <c r="D6" t="n">
-        <v>0.417211</v>
+        <v>0.311243</v>
       </c>
       <c r="E6" t="n">
-        <v>135.357001</v>
+        <v>0.578161</v>
       </c>
       <c r="F6" t="n">
-        <v>0.854248</v>
+        <v>0.73783</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>OLS</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -9042,7 +9042,7 @@
         <v>0.417211</v>
       </c>
       <c r="E7" t="n">
-        <v>135.357001</v>
+        <v>0.679094</v>
       </c>
       <c r="F7" t="n">
         <v>0.854248</v>
@@ -9051,22 +9051,44 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.073737</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.09384199999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.417211</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.679094</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.854248</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>OLS+Dummy</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>0.07393</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>0.094011</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>0.418712</v>
       </c>
-      <c r="E8" t="n">
-        <v>135.574051</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="E9" t="n">
+        <v>0.680873</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.855783</v>
       </c>
     </row>
@@ -9081,7 +9103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9112,7 +9134,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>sMAPE(%)</t>
+          <t>MASE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -9124,26 +9146,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GARCH(1,1)</t>
+          <t>GARCH-t</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.062705</v>
+        <v>0.061965</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08096200000000001</v>
+        <v>0.079566</v>
       </c>
       <c r="E2" t="n">
-        <v>0.310539</v>
+        <v>0.299928</v>
       </c>
       <c r="F2" t="n">
-        <v>132.454442</v>
+        <v>0.570679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.736994</v>
+        <v>0.724294</v>
       </c>
     </row>
     <row r="3">
@@ -9153,7 +9175,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="C3" t="n">
         <v>0.063593</v>
@@ -9165,7 +9187,7 @@
         <v>0.297974</v>
       </c>
       <c r="F3" t="n">
-        <v>195.696124</v>
+        <v>0.5856749999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0.721931</v>
@@ -9174,26 +9196,26 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ARCH(1)</t>
+          <t>GARCH(1,1)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.062777</v>
+        <v>0.062705</v>
       </c>
       <c r="D4" t="n">
-        <v>0.081053</v>
+        <v>0.08096200000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.311243</v>
+        <v>0.310539</v>
       </c>
       <c r="F4" t="n">
-        <v>132.131178</v>
+        <v>0.577494</v>
       </c>
       <c r="G4" t="n">
-        <v>0.73783</v>
+        <v>0.736994</v>
       </c>
     </row>
     <row r="5">
@@ -9203,7 +9225,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="C5" t="n">
         <v>0.065065</v>
@@ -9215,7 +9237,7 @@
         <v>0.309942</v>
       </c>
       <c r="F5" t="n">
-        <v>171.127489</v>
+        <v>0.599224</v>
       </c>
       <c r="G5" t="n">
         <v>0.736286</v>
@@ -9224,36 +9246,36 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OLS</t>
+          <t>ARCH(1)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.073737</v>
+        <v>0.062777</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09384199999999999</v>
+        <v>0.081053</v>
       </c>
       <c r="E6" t="n">
-        <v>0.417211</v>
+        <v>0.311243</v>
       </c>
       <c r="F6" t="n">
-        <v>135.357001</v>
+        <v>0.578161</v>
       </c>
       <c r="G6" t="n">
-        <v>0.854248</v>
+        <v>0.73783</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>OLS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
         <v>0.073737</v>
@@ -9265,7 +9287,7 @@
         <v>0.417211</v>
       </c>
       <c r="F7" t="n">
-        <v>135.357001</v>
+        <v>0.679094</v>
       </c>
       <c r="G7" t="n">
         <v>0.854248</v>
@@ -9274,25 +9296,50 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.073737</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.09384199999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.417211</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.679094</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.854248</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>OLS+Dummy</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.07393</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>0.094011</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>0.418712</v>
       </c>
-      <c r="F8" t="n">
-        <v>135.574051</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F9" t="n">
+        <v>0.680873</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.855783</v>
       </c>
     </row>
@@ -9307,7 +9354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9340,7 +9387,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>GARCH-t</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9349,10 +9396,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.8025</v>
+        <v>-0.1724</v>
       </c>
       <c r="D2" t="n">
-        <v>0.422277</v>
+        <v>0.8630949999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -9363,7 +9410,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GARCH(1,1)</t>
+          <t>SARIMA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9372,10 +9419,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.6253</v>
+        <v>-0.8025</v>
       </c>
       <c r="D3" t="n">
-        <v>0.531747</v>
+        <v>0.422277</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -9386,7 +9433,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARCH(1)</t>
+          <t>GARCH(1,1)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9395,10 +9442,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.6469</v>
+        <v>-0.6253</v>
       </c>
       <c r="D4" t="n">
-        <v>0.517727</v>
+        <v>0.531747</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -9409,7 +9456,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OLS</t>
+          <t>ARCH(1)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9418,10 +9465,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1.8366</v>
+        <v>-0.6469</v>
       </c>
       <c r="D5" t="n">
-        <v>0.066265</v>
+        <v>0.517727</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -9432,7 +9479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>OLS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9455,21 +9502,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.8366</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.066265</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No sig. difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>OLS+Dummy</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ARIMA</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C8" t="n">
         <v>-1.8546</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>0.06365999999999999</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>No sig. difference</t>
         </is>
@@ -9536,19 +9606,19 @@
         <v>44227</v>
       </c>
       <c r="C2" t="n">
-        <v>47.431</v>
+        <v>46.6051</v>
       </c>
       <c r="D2" t="n">
-        <v>46.1229</v>
+        <v>45.6731</v>
       </c>
       <c r="E2" t="n">
-        <v>48.7763</v>
+        <v>47.5562</v>
       </c>
       <c r="F2" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="3">
@@ -9561,19 +9631,19 @@
         <v>44255</v>
       </c>
       <c r="C3" t="n">
-        <v>48.0295</v>
+        <v>42.406</v>
       </c>
       <c r="D3" t="n">
-        <v>45.4167</v>
+        <v>40.7268</v>
       </c>
       <c r="E3" t="n">
-        <v>50.7926</v>
+        <v>44.1544</v>
       </c>
       <c r="F3" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="4">
@@ -9586,19 +9656,19 @@
         <v>44286</v>
       </c>
       <c r="C4" t="n">
-        <v>48.6356</v>
+        <v>38.5852</v>
       </c>
       <c r="D4" t="n">
-        <v>44.7214</v>
+        <v>36.3162</v>
       </c>
       <c r="E4" t="n">
-        <v>52.8923</v>
+        <v>40.996</v>
       </c>
       <c r="F4" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="5">
@@ -9611,19 +9681,19 @@
         <v>44316</v>
       </c>
       <c r="C5" t="n">
-        <v>49.2493</v>
+        <v>35.1087</v>
       </c>
       <c r="D5" t="n">
-        <v>44.0367</v>
+        <v>32.3833</v>
       </c>
       <c r="E5" t="n">
-        <v>55.0788</v>
+        <v>38.0635</v>
       </c>
       <c r="F5" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="6">
@@ -9636,19 +9706,19 @@
         <v>44347</v>
       </c>
       <c r="C6" t="n">
-        <v>49.8707</v>
+        <v>31.9455</v>
       </c>
       <c r="D6" t="n">
-        <v>43.3625</v>
+        <v>28.8763</v>
       </c>
       <c r="E6" t="n">
-        <v>57.3557</v>
+        <v>35.3408</v>
       </c>
       <c r="F6" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="7">
@@ -9661,19 +9731,19 @@
         <v>44377</v>
       </c>
       <c r="C7" t="n">
-        <v>50.5</v>
+        <v>29.0672</v>
       </c>
       <c r="D7" t="n">
-        <v>42.6986</v>
+        <v>25.7491</v>
       </c>
       <c r="E7" t="n">
-        <v>59.7267</v>
+        <v>32.8128</v>
       </c>
       <c r="F7" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="8">
@@ -9686,19 +9756,19 @@
         <v>44408</v>
       </c>
       <c r="C8" t="n">
-        <v>51.1372</v>
+        <v>26.4482</v>
       </c>
       <c r="D8" t="n">
-        <v>42.0448</v>
+        <v>22.9606</v>
       </c>
       <c r="E8" t="n">
-        <v>62.1957</v>
+        <v>30.4657</v>
       </c>
       <c r="F8" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="9">
@@ -9711,19 +9781,19 @@
         <v>44439</v>
       </c>
       <c r="C9" t="n">
-        <v>51.7824</v>
+        <v>24.0653</v>
       </c>
       <c r="D9" t="n">
-        <v>41.4011</v>
+        <v>20.474</v>
       </c>
       <c r="E9" t="n">
-        <v>64.7668</v>
+        <v>28.2864</v>
       </c>
       <c r="F9" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="10">
@@ -9736,19 +9806,19 @@
         <v>44469</v>
       </c>
       <c r="C10" t="n">
-        <v>52.4358</v>
+        <v>21.897</v>
       </c>
       <c r="D10" t="n">
-        <v>40.7673</v>
+        <v>18.2568</v>
       </c>
       <c r="E10" t="n">
-        <v>67.4442</v>
+        <v>26.2631</v>
       </c>
       <c r="F10" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="11">
@@ -9761,19 +9831,19 @@
         <v>44500</v>
       </c>
       <c r="C11" t="n">
-        <v>53.0975</v>
+        <v>19.9241</v>
       </c>
       <c r="D11" t="n">
-        <v>40.1431</v>
+        <v>16.2796</v>
       </c>
       <c r="E11" t="n">
-        <v>70.23220000000001</v>
+        <v>24.3845</v>
       </c>
       <c r="F11" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="12">
@@ -9786,19 +9856,19 @@
         <v>44530</v>
       </c>
       <c r="C12" t="n">
-        <v>53.7675</v>
+        <v>18.1289</v>
       </c>
       <c r="D12" t="n">
-        <v>39.5285</v>
+        <v>14.5166</v>
       </c>
       <c r="E12" t="n">
-        <v>73.13549999999999</v>
+        <v>22.6402</v>
       </c>
       <c r="F12" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="13">
@@ -9811,19 +9881,19 @@
         <v>44561</v>
       </c>
       <c r="C13" t="n">
-        <v>54.4459</v>
+        <v>16.4955</v>
       </c>
       <c r="D13" t="n">
-        <v>38.9233</v>
+        <v>12.9445</v>
       </c>
       <c r="E13" t="n">
-        <v>76.1589</v>
+        <v>21.0207</v>
       </c>
       <c r="F13" t="n">
-        <v>0.012539</v>
+        <v>-0.09442</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.015</v>
+        <v>-0.1219591887516287</v>
       </c>
     </row>
     <row r="14">
@@ -9836,13 +9906,13 @@
         <v>44227</v>
       </c>
       <c r="C14" t="n">
-        <v>48.1479</v>
+        <v>52.6502</v>
       </c>
       <c r="D14" t="n">
-        <v>47.2584</v>
+        <v>51.9458</v>
       </c>
       <c r="E14" t="n">
-        <v>49.054</v>
+        <v>53.364</v>
       </c>
       <c r="F14" t="n">
         <v>0.027539</v>
@@ -9861,13 +9931,13 @@
         <v>44255</v>
       </c>
       <c r="C15" t="n">
-        <v>49.4922</v>
+        <v>54.1202</v>
       </c>
       <c r="D15" t="n">
-        <v>47.6806</v>
+        <v>52.682</v>
       </c>
       <c r="E15" t="n">
-        <v>51.3727</v>
+        <v>55.5978</v>
       </c>
       <c r="F15" t="n">
         <v>0.027539</v>
@@ -9886,13 +9956,13 @@
         <v>44286</v>
       </c>
       <c r="C16" t="n">
-        <v>50.8742</v>
+        <v>55.6314</v>
       </c>
       <c r="D16" t="n">
-        <v>48.1066</v>
+        <v>53.4285</v>
       </c>
       <c r="E16" t="n">
-        <v>53.8009</v>
+        <v>57.9251</v>
       </c>
       <c r="F16" t="n">
         <v>0.027539</v>
@@ -9911,13 +9981,13 @@
         <v>44316</v>
       </c>
       <c r="C17" t="n">
-        <v>52.2947</v>
+        <v>57.1847</v>
       </c>
       <c r="D17" t="n">
-        <v>48.5364</v>
+        <v>54.1856</v>
       </c>
       <c r="E17" t="n">
-        <v>56.344</v>
+        <v>60.3498</v>
       </c>
       <c r="F17" t="n">
         <v>0.027539</v>
@@ -9936,13 +10006,13 @@
         <v>44347</v>
       </c>
       <c r="C18" t="n">
-        <v>53.7548</v>
+        <v>58.7814</v>
       </c>
       <c r="D18" t="n">
-        <v>48.97</v>
+        <v>54.9535</v>
       </c>
       <c r="E18" t="n">
-        <v>59.0072</v>
+        <v>62.876</v>
       </c>
       <c r="F18" t="n">
         <v>0.027539</v>
@@ -9961,13 +10031,13 @@
         <v>44377</v>
       </c>
       <c r="C19" t="n">
-        <v>55.2558</v>
+        <v>60.4227</v>
       </c>
       <c r="D19" t="n">
-        <v>49.4074</v>
+        <v>55.7322</v>
       </c>
       <c r="E19" t="n">
-        <v>61.7963</v>
+        <v>65.50790000000001</v>
       </c>
       <c r="F19" t="n">
         <v>0.027539</v>
@@ -9986,13 +10056,13 @@
         <v>44408</v>
       </c>
       <c r="C20" t="n">
-        <v>56.7986</v>
+        <v>62.1098</v>
       </c>
       <c r="D20" t="n">
-        <v>49.8488</v>
+        <v>56.522</v>
       </c>
       <c r="E20" t="n">
-        <v>64.71729999999999</v>
+        <v>68.2501</v>
       </c>
       <c r="F20" t="n">
         <v>0.027539</v>
@@ -10011,13 +10081,13 @@
         <v>44439</v>
       </c>
       <c r="C21" t="n">
-        <v>58.3845</v>
+        <v>63.844</v>
       </c>
       <c r="D21" t="n">
-        <v>50.2942</v>
+        <v>57.323</v>
       </c>
       <c r="E21" t="n">
-        <v>67.77630000000001</v>
+        <v>71.107</v>
       </c>
       <c r="F21" t="n">
         <v>0.027539</v>
@@ -10036,13 +10106,13 @@
         <v>44469</v>
       </c>
       <c r="C22" t="n">
-        <v>60.0147</v>
+        <v>65.6267</v>
       </c>
       <c r="D22" t="n">
-        <v>50.7435</v>
+        <v>58.1353</v>
       </c>
       <c r="E22" t="n">
-        <v>70.9799</v>
+        <v>74.0834</v>
       </c>
       <c r="F22" t="n">
         <v>0.027539</v>
@@ -10061,13 +10131,13 @@
         <v>44500</v>
       </c>
       <c r="C23" t="n">
-        <v>61.6905</v>
+        <v>67.45910000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>51.1968</v>
+        <v>58.9591</v>
       </c>
       <c r="E23" t="n">
-        <v>74.33499999999999</v>
+        <v>77.1845</v>
       </c>
       <c r="F23" t="n">
         <v>0.027539</v>
@@ -10086,13 +10156,13 @@
         <v>44530</v>
       </c>
       <c r="C24" t="n">
-        <v>63.413</v>
+        <v>69.34269999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>51.6542</v>
+        <v>59.7946</v>
       </c>
       <c r="E24" t="n">
-        <v>77.8486</v>
+        <v>80.41540000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0.027539</v>
@@ -10111,13 +10181,13 @@
         <v>44561</v>
       </c>
       <c r="C25" t="n">
-        <v>65.1836</v>
+        <v>71.27889999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>52.1156</v>
+        <v>60.642</v>
       </c>
       <c r="E25" t="n">
-        <v>81.5283</v>
+        <v>83.7816</v>
       </c>
       <c r="F25" t="n">
         <v>0.027539</v>
@@ -10136,19 +10206,19 @@
         <v>44227</v>
       </c>
       <c r="C26" t="n">
-        <v>48.8755</v>
+        <v>59.4793</v>
       </c>
       <c r="D26" t="n">
-        <v>48.1968</v>
+        <v>58.8815</v>
       </c>
       <c r="E26" t="n">
-        <v>49.5638</v>
+        <v>60.0831</v>
       </c>
       <c r="F26" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G26" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="27">
@@ -10161,19 +10231,19 @@
         <v>44255</v>
       </c>
       <c r="C27" t="n">
-        <v>50.9995</v>
+        <v>69.07040000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>49.5929</v>
+        <v>67.6891</v>
       </c>
       <c r="E27" t="n">
-        <v>52.446</v>
+        <v>70.48</v>
       </c>
       <c r="F27" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G27" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="28">
@@ -10186,19 +10256,19 @@
         <v>44286</v>
       </c>
       <c r="C28" t="n">
-        <v>53.2158</v>
+        <v>80.2081</v>
       </c>
       <c r="D28" t="n">
-        <v>51.0295</v>
+        <v>77.8141</v>
       </c>
       <c r="E28" t="n">
-        <v>55.4958</v>
+        <v>82.6758</v>
       </c>
       <c r="F28" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G28" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="29">
@@ -10211,19 +10281,19 @@
         <v>44316</v>
       </c>
       <c r="C29" t="n">
-        <v>55.5284</v>
+        <v>93.1418</v>
       </c>
       <c r="D29" t="n">
-        <v>52.5076</v>
+        <v>89.45359999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>58.7229</v>
+        <v>96.9821</v>
       </c>
       <c r="F29" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G29" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="30">
@@ -10236,19 +10306,19 @@
         <v>44347</v>
       </c>
       <c r="C30" t="n">
-        <v>57.9415</v>
+        <v>108.1611</v>
       </c>
       <c r="D30" t="n">
-        <v>54.0286</v>
+        <v>102.8342</v>
       </c>
       <c r="E30" t="n">
-        <v>62.1377</v>
+        <v>113.764</v>
       </c>
       <c r="F30" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G30" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="31">
@@ -10261,19 +10331,19 @@
         <v>44377</v>
       </c>
       <c r="C31" t="n">
-        <v>60.4594</v>
+        <v>125.6023</v>
       </c>
       <c r="D31" t="n">
-        <v>55.5936</v>
+        <v>118.2162</v>
       </c>
       <c r="E31" t="n">
-        <v>65.75109999999999</v>
+        <v>133.4497</v>
       </c>
       <c r="F31" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G31" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="32">
@@ -10286,19 +10356,19 @@
         <v>44408</v>
       </c>
       <c r="C32" t="n">
-        <v>63.0868</v>
+        <v>145.8558</v>
       </c>
       <c r="D32" t="n">
-        <v>57.204</v>
+        <v>135.8991</v>
       </c>
       <c r="E32" t="n">
-        <v>69.5746</v>
+        <v>156.542</v>
       </c>
       <c r="F32" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G32" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="33">
@@ -10311,19 +10381,19 @@
         <v>44439</v>
       </c>
       <c r="C33" t="n">
-        <v>65.8284</v>
+        <v>169.3753</v>
       </c>
       <c r="D33" t="n">
-        <v>58.861</v>
+        <v>156.2271</v>
       </c>
       <c r="E33" t="n">
-        <v>73.6204</v>
+        <v>183.6301</v>
       </c>
       <c r="F33" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G33" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="34">
@@ -10336,19 +10406,19 @@
         <v>44469</v>
       </c>
       <c r="C34" t="n">
-        <v>68.6891</v>
+        <v>196.6873</v>
       </c>
       <c r="D34" t="n">
-        <v>60.5661</v>
+        <v>179.5957</v>
       </c>
       <c r="E34" t="n">
-        <v>77.9015</v>
+        <v>215.4055</v>
       </c>
       <c r="F34" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G34" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="35">
@@ -10361,19 +10431,19 @@
         <v>44500</v>
       </c>
       <c r="C35" t="n">
-        <v>71.6741</v>
+        <v>228.4034</v>
       </c>
       <c r="D35" t="n">
-        <v>62.3205</v>
+        <v>206.4598</v>
       </c>
       <c r="E35" t="n">
-        <v>82.4316</v>
+        <v>252.6794</v>
       </c>
       <c r="F35" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G35" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="36">
@@ -10386,19 +10456,19 @@
         <v>44530</v>
       </c>
       <c r="C36" t="n">
-        <v>74.78879999999999</v>
+        <v>265.2339</v>
       </c>
       <c r="D36" t="n">
-        <v>64.12569999999999</v>
+        <v>237.3422</v>
       </c>
       <c r="E36" t="n">
-        <v>87.22499999999999</v>
+        <v>296.4032</v>
       </c>
       <c r="F36" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G36" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
     <row r="37">
@@ -10411,19 +10481,19 @@
         <v>44561</v>
       </c>
       <c r="C37" t="n">
-        <v>78.0389</v>
+        <v>308.0032</v>
       </c>
       <c r="D37" t="n">
-        <v>65.9832</v>
+        <v>272.8441</v>
       </c>
       <c r="E37" t="n">
-        <v>92.29730000000001</v>
+        <v>347.693</v>
       </c>
       <c r="F37" t="n">
-        <v>0.042539</v>
+        <v>0.149498</v>
       </c>
       <c r="G37" t="n">
-        <v>0.015</v>
+        <v>0.1219591887516287</v>
       </c>
     </row>
   </sheetData>
@@ -10556,7 +10626,7 @@
         <v>0.09191000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.091146</v>
+        <v>0.091789</v>
       </c>
       <c r="E6" t="n">
         <v>0.088862</v>
@@ -10594,7 +10664,7 @@
         <v>0.056042</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05746</v>
+        <v>0.057302</v>
       </c>
       <c r="E8" t="n">
         <v>0.07189</v>
@@ -10613,7 +10683,7 @@
         <v>0.075186</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07999100000000001</v>
+        <v>0.079983</v>
       </c>
       <c r="E9" t="n">
         <v>0.104848</v>
@@ -11967,7 +12037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12013,20 +12083,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>GARCH-t</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>OLS+Dummy</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>GARCH_Vol_Forecast</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>GARCH_Vol_Normal</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GARCH_Vol_t</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Bootstrap_PI_Lo</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Bootstrap_PI_Hi</t>
         </is>
@@ -12058,16 +12138,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I2" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J2" t="n">
         <v>-0.003083664718185886</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.118080579539319</v>
       </c>
-      <c r="K2" t="n">
-        <v>-0.02295661173313064</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01575317833229062</v>
+        <v>0.1205334555720676</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.01546486603359802</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.007751731984722898</v>
       </c>
     </row>
     <row r="3">
@@ -12096,16 +12182,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I3" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.005163716767816668</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.1328836710226488</v>
       </c>
-      <c r="K3" t="n">
-        <v>-0.05766415653099283</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.06421709878707839</v>
+        <v>0.1370799941955598</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.04774665298168298</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.06576212297306697</v>
       </c>
     </row>
     <row r="4">
@@ -12134,16 +12226,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I4" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.01710334577820875</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.1576919362224942</v>
       </c>
-      <c r="K4" t="n">
-        <v>-0.05401829191957107</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.09648285876712288</v>
+        <v>0.1645056077525832</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.04726498816843342</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.07843789549280306</v>
       </c>
     </row>
     <row r="5">
@@ -12172,16 +12270,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I5" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.1089208464775091</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.187478179745587</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.07504551641237388</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1444719940298593</v>
+        <v>0.1971263285956566</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.08175118601877461</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1361181404115201</v>
       </c>
     </row>
     <row r="6">
@@ -12210,16 +12314,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I6" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.09785443111743369</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.2189113449732759</v>
       </c>
-      <c r="K6" t="n">
-        <v>0.05014635485880805</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1467477982649042</v>
+        <v>0.2313345761105931</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.05896089922738997</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1403296755623085</v>
       </c>
     </row>
     <row r="7">
@@ -12248,16 +12358,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I7" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.05598135602119456</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.2500088467048501</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.0004180121483786268</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1163240273790106</v>
+        <v>0.2650419272401702</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.01126087928272843</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.09692196641763949</v>
       </c>
     </row>
     <row r="8">
@@ -12286,16 +12402,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I8" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.04655928169461227</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0.2795814980040822</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.02030939875274044</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.07531875416671258</v>
+        <v>0.2970134011114392</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.02509338646375015</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.06362084882799884</v>
       </c>
     </row>
     <row r="9">
@@ -12324,16 +12446,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I9" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.005037537657807533</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>0.3069078980951154</v>
       </c>
-      <c r="K9" t="n">
-        <v>-0.01798508199699158</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.02457985915399221</v>
+        <v>0.3265054149380867</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.008683405426871986</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.01774867884651286</v>
       </c>
     </row>
     <row r="10">
@@ -12362,16 +12490,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I10" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J10" t="n">
         <v>0.0005185078334792662</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>0.3315680802382587</v>
       </c>
-      <c r="K10" t="n">
-        <v>-0.04100034530410715</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.03495173726689044</v>
+        <v>0.3530883459744255</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.03131768857334537</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.03377389958042163</v>
       </c>
     </row>
     <row r="11">
@@ -12400,16 +12534,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I11" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.1201496581044347</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>0.3533551393159042</v>
       </c>
-      <c r="K11" t="n">
-        <v>0.05746429341639468</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1810985343481542</v>
+        <v>0.3765544822075458</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.07206670254281987</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1693744816915624</v>
       </c>
     </row>
     <row r="12">
@@ -12438,16 +12578,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I12" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.04185623276120064</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>0.3722221149840347</v>
       </c>
-      <c r="K12" t="n">
-        <v>-0.01772670253164925</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.09579308881952169</v>
+        <v>0.3968632342886293</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.004647762897291699</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.08804746109021958</v>
       </c>
     </row>
     <row r="13">
@@ -12476,16 +12622,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I13" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.09687441382817275</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>0.3882445033439669</v>
       </c>
-      <c r="K13" t="n">
-        <v>0.05742836688976386</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1306444750175876</v>
+        <v>0.4141024046090784</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.06723880710549444</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1275252488941827</v>
       </c>
     </row>
     <row r="14">
@@ -12514,16 +12666,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I14" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J14" t="n">
         <v>0.05532198784401465</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>0.4015898402238609</v>
       </c>
-      <c r="K14" t="n">
-        <v>0.01745639321843244</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.08778276143282063</v>
+        <v>0.4284565279006993</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.02788392434127557</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.08192066410321798</v>
       </c>
     </row>
     <row r="15">
@@ -12552,16 +12710,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I15" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.08124232884826772</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>0.4124909457865659</v>
       </c>
-      <c r="K15" t="n">
-        <v>0.03835349083044496</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1194708980912759</v>
+        <v>0.44017880445634</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.05007798505511667</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1118894659618781</v>
       </c>
     </row>
     <row r="16">
@@ -12590,16 +12754,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I16" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.158675876411472</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>0.4212218147250169</v>
       </c>
-      <c r="K16" t="n">
-        <v>0.06099578995842677</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.2590763791227568</v>
+        <v>0.4495656576909284</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.07299650702492726</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2384751066720755</v>
       </c>
     </row>
     <row r="17">
@@ -12628,16 +12798,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I17" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J17" t="n">
         <v>-0.06673877594473858</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>0.428076207711919</v>
       </c>
-      <c r="K17" t="n">
-        <v>-0.1290000082413751</v>
-      </c>
       <c r="L17" t="n">
-        <v>-0.004984729547165132</v>
+        <v>0.4569340518092664</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.1272126684259837</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.01424819660140873</v>
       </c>
     </row>
     <row r="18">
@@ -12666,16 +12842,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I18" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.1702112768138139</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>0.4333493903712887</v>
       </c>
-      <c r="K18" t="n">
-        <v>0.07330214561210766</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.2580027832628181</v>
+        <v>0.4626020954433815</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.08939814430541054</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2485013358227392</v>
       </c>
     </row>
     <row r="19">
@@ -12704,16 +12886,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I19" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.09274428993608248</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>0.4373234834469942</v>
       </c>
-      <c r="K19" t="n">
-        <v>0.006125795779323481</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1766141075426121</v>
+        <v>0.4668734584180452</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.01334834431277774</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1648483950357832</v>
       </c>
     </row>
     <row r="20">
@@ -12742,16 +12930,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I20" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J20" t="n">
         <v>-0.02903250041576957</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>0.4402566998542026</v>
       </c>
-      <c r="K20" t="n">
-        <v>-0.06964509368073138</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.008437044358539914</v>
+        <v>0.4700259168291918</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.06999240104501744</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.004623327545456521</v>
       </c>
     </row>
     <row r="21">
@@ -12780,16 +12974,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I21" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J21" t="n">
         <v>-0.04095138040024565</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>0.4423764603801197</v>
       </c>
-      <c r="K21" t="n">
-        <v>-0.08248946836964807</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.0001453867687107253</v>
+        <v>0.4723040308032185</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.08104897805407198</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.005703453300046914</v>
       </c>
     </row>
     <row r="22">
@@ -12818,16 +13018,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I22" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J22" t="n">
         <v>-0.05135421558589742</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>0.4438760820597984</v>
       </c>
-      <c r="K22" t="n">
-        <v>-0.09587758007762479</v>
-      </c>
       <c r="L22" t="n">
-        <v>-0.005256571553798934</v>
+        <v>0.4739156359090653</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.09288505273244378</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.01691931544488882</v>
       </c>
     </row>
     <row r="23">
@@ -12856,16 +13062,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I23" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J23" t="n">
         <v>0.05961781470354979</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>0.44491448417364</v>
       </c>
-      <c r="K23" t="n">
-        <v>0.02475218669295816</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.09110643867758959</v>
+        <v>0.4750315592293518</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.0342246118200012</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.08353153761983814</v>
       </c>
     </row>
     <row r="24">
@@ -12894,16 +13106,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I24" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J24" t="n">
         <v>0.118609326087778</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>0.4456181974341654</v>
       </c>
-      <c r="K24" t="n">
-        <v>0.06346152734059521</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.1618451568882685</v>
+        <v>0.4757877980746685</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.07845659551418849</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.1590710819157851</v>
       </c>
     </row>
     <row r="25">
@@ -12932,16 +13150,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I25" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J25" t="n">
         <v>0.03780517987831862</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>0.4460849088090517</v>
       </c>
-      <c r="K25" t="n">
-        <v>-0.008040085971993476</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.07881001068437721</v>
+        <v>0.4762893407902744</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.001019784170336726</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.07323907856429739</v>
       </c>
     </row>
     <row r="26">
@@ -12970,16 +13194,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I26" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J26" t="n">
         <v>0.1120174819549735</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>0.4463878202788691</v>
       </c>
-      <c r="K26" t="n">
-        <v>0.08257632709403652</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.1453031193088614</v>
+        <v>0.476614857157945</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.08790982515092267</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.136247483268073</v>
       </c>
     </row>
     <row r="27">
@@ -13008,16 +13238,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I27" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J27" t="n">
         <v>-0.02816641867351705</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>0.4465802192746454</v>
       </c>
-      <c r="K27" t="n">
-        <v>-0.05893266783019199</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.003561348648228092</v>
+        <v>0.4768216132682832</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.05526542830425393</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.006499943367357652</v>
       </c>
     </row>
     <row r="28">
@@ -13046,16 +13282,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I28" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J28" t="n">
         <v>0.04570774374062817</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>0.4466998173976346</v>
       </c>
-      <c r="K28" t="n">
-        <v>0.01861572880868748</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.06935014075202829</v>
+        <v>0.4769501357001342</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.02825568101421861</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.06427611503433502</v>
       </c>
     </row>
     <row r="29">
@@ -13084,16 +13326,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I29" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J29" t="n">
         <v>0.03093535995427081</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>0.4467725789322987</v>
       </c>
-      <c r="K29" t="n">
-        <v>0.01208309668399163</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.04726420122834808</v>
+        <v>0.4770283265288831</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.01895372660225652</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.04114906508652931</v>
       </c>
     </row>
     <row r="30">
@@ -13122,16 +13370,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I30" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J30" t="n">
         <v>-0.03700939340858017</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>0.4468159061603341</v>
       </c>
-      <c r="K30" t="n">
-        <v>-0.05973835703264076</v>
-      </c>
       <c r="L30" t="n">
-        <v>-0.01637931548019706</v>
+        <v>0.4770748866933162</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-0.05669908350299847</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.02120488932982835</v>
       </c>
     </row>
     <row r="31">
@@ -13160,16 +13414,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I31" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J31" t="n">
         <v>0.05162718652424251</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>0.4468411601132367</v>
       </c>
-      <c r="K31" t="n">
-        <v>0.02006879865280256</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.07468663167155683</v>
+        <v>0.4771020250002908</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.03059287510917945</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.07492636442578123</v>
       </c>
     </row>
     <row r="32">
@@ -13198,16 +13458,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I32" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J32" t="n">
         <v>0.04442054400498961</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>0.4468555691772118</v>
       </c>
-      <c r="K32" t="n">
-        <v>0.02061951257176475</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.0691422586111828</v>
+        <v>0.4771175092094388</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.02774652446199937</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.05992082382106204</v>
       </c>
     </row>
     <row r="33">
@@ -13236,16 +13502,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I33" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J33" t="n">
         <v>-0.01135686772901846</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>0.4468636175539338</v>
       </c>
-      <c r="K33" t="n">
-        <v>-0.05003448935958187</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.02379560416263245</v>
+        <v>0.477126158121555</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.04374871408422969</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.01653083916236618</v>
       </c>
     </row>
     <row r="34">
@@ -13274,16 +13546,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I34" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J34" t="n">
         <v>-0.0167266789168843</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>0.4468680187842246</v>
       </c>
-      <c r="K34" t="n">
-        <v>-0.04801748462480998</v>
-      </c>
       <c r="L34" t="n">
-        <v>0.01439132061404266</v>
+        <v>0.4771308877523614</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.0437846506564598</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.004610687768341016</v>
       </c>
     </row>
     <row r="35">
@@ -13312,16 +13590,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I35" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J35" t="n">
         <v>-0.03545400163389129</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>0.446870375237736</v>
       </c>
-      <c r="K35" t="n">
-        <v>-0.05731566184071327</v>
-      </c>
       <c r="L35" t="n">
-        <v>-0.01656893390631568</v>
+        <v>0.4771334200339776</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.05228503757264107</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-0.0185745592724075</v>
       </c>
     </row>
     <row r="36">
@@ -13350,16 +13634,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I36" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J36" t="n">
         <v>0.08618405680351315</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>0.4468716105784005</v>
       </c>
-      <c r="K36" t="n">
-        <v>0.04675983045871443</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.1188088125217544</v>
+        <v>0.4771347475502436</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.05827305034035384</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.1170329428039171</v>
       </c>
     </row>
     <row r="37">
@@ -13388,16 +13678,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I37" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J37" t="n">
         <v>0.05202208555129566</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>0.4468722447110156</v>
       </c>
-      <c r="K37" t="n">
-        <v>0.0244625969368752</v>
-      </c>
       <c r="L37" t="n">
-        <v>0.07470627868819558</v>
+        <v>0.4771354289989906</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.03575390464988988</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.06947517569063513</v>
       </c>
     </row>
     <row r="38">
@@ -13426,16 +13722,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I38" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J38" t="n">
         <v>-0.02406966510929609</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>0.446872563467995</v>
       </c>
-      <c r="K38" t="n">
-        <v>-0.06468541550806656</v>
-      </c>
       <c r="L38" t="n">
-        <v>0.01202991567990592</v>
+        <v>0.4771357715401833</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-0.0566937783417187</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.007042874530250647</v>
       </c>
     </row>
     <row r="39">
@@ -13464,16 +13766,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I39" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J39" t="n">
         <v>0.01644884271430614</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>0.4468727203758834</v>
       </c>
-      <c r="K39" t="n">
-        <v>-0.01595049982701446</v>
-      </c>
       <c r="L39" t="n">
-        <v>0.04722692187471794</v>
+        <v>0.4771359401558322</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-0.006453651074311491</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.03890208854828783</v>
       </c>
     </row>
     <row r="40">
@@ -13502,16 +13810,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I40" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J40" t="n">
         <v>0.04415762841415772</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>0.4468727960161522</v>
       </c>
-      <c r="K40" t="n">
-        <v>0.01918948926780285</v>
-      </c>
       <c r="L40" t="n">
-        <v>0.0671604634396232</v>
+        <v>0.477136021440037</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.02743647030188574</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.06000095567853898</v>
       </c>
     </row>
     <row r="41">
@@ -13540,16 +13854,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I41" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J41" t="n">
         <v>-0.03601719118850925</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>0.4468728317270663</v>
       </c>
-      <c r="K41" t="n">
-        <v>-0.06145924284064294</v>
-      </c>
       <c r="L41" t="n">
-        <v>-0.01418234792801719</v>
+        <v>0.4771360598155386</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-0.05470756240500693</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-0.02004739596142224</v>
       </c>
     </row>
     <row r="42">
@@ -13578,16 +13898,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I42" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J42" t="n">
         <v>0.00823870051725172</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>0.4468728482392181</v>
       </c>
-      <c r="K42" t="n">
-        <v>-0.01798351160328217</v>
-      </c>
       <c r="L42" t="n">
-        <v>0.03123093230300877</v>
+        <v>0.4771360775597526</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-0.007913580010787355</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.02372753365345772</v>
       </c>
     </row>
     <row r="43">
@@ -13616,16 +13942,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I43" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J43" t="n">
         <v>-0.07381671480433301</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>0.4468728557170423</v>
       </c>
-      <c r="K43" t="n">
-        <v>-0.09667682512298273</v>
-      </c>
       <c r="L43" t="n">
-        <v>-0.0524290612353507</v>
+        <v>0.4771360855955383</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-0.0931727611575358</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-0.05897671108494116</v>
       </c>
     </row>
     <row r="44">
@@ -13654,16 +13986,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I44" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J44" t="n">
         <v>0.01876167276642249</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>0.4468728590339147</v>
       </c>
-      <c r="K44" t="n">
-        <v>-0.008361803356105525</v>
-      </c>
       <c r="L44" t="n">
-        <v>0.04056567028029802</v>
+        <v>0.4771360891599006</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-0.001142055930128552</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.0390002511425321</v>
       </c>
     </row>
     <row r="45">
@@ -13692,16 +14030,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I45" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J45" t="n">
         <v>0.03286861309117416</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>0.4468728604749556</v>
       </c>
-      <c r="K45" t="n">
-        <v>0.01128371346606107</v>
-      </c>
       <c r="L45" t="n">
-        <v>0.05393901891147791</v>
+        <v>0.4771360907084656</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.01941216108467229</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.04593895478108092</v>
       </c>
     </row>
     <row r="46">
@@ -13730,16 +14074,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I46" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.03449572869603283</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>0.4468728610881939</v>
       </c>
-      <c r="K46" t="n">
-        <v>0.0113295622282692</v>
-      </c>
       <c r="L46" t="n">
-        <v>0.05281728270538875</v>
+        <v>0.4771360913674609</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.02044464354643739</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.05112463433031408</v>
       </c>
     </row>
     <row r="47">
@@ -13768,16 +14118,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I47" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J47" t="n">
         <v>-0.06484780188404649</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>0.4468728613438158</v>
       </c>
-      <c r="K47" t="n">
-        <v>-0.1017546621226135</v>
-      </c>
       <c r="L47" t="n">
-        <v>-0.02778606203329142</v>
+        <v>0.4771360916421562</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-0.0975324635206956</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-0.03594784303854195</v>
       </c>
     </row>
     <row r="48">
@@ -13806,16 +14162,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I48" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J48" t="n">
         <v>-0.0228256169038855</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>0.4468728614481899</v>
       </c>
-      <c r="K48" t="n">
-        <v>-0.04863897354271271</v>
-      </c>
       <c r="L48" t="n">
-        <v>-0.0001377696640011448</v>
+        <v>0.4771360917543182</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-0.04373222371584742</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-0.006217340797640797</v>
       </c>
     </row>
     <row r="49">
@@ -13844,16 +14206,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I49" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J49" t="n">
         <v>-0.03719125050568699</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>0.4468728614899365</v>
       </c>
-      <c r="K49" t="n">
-        <v>-0.07657813273719834</v>
-      </c>
       <c r="L49" t="n">
-        <v>0.004557497343983509</v>
+        <v>0.4771360917991798</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-0.07118448250079096</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-0.007530137783723851</v>
       </c>
     </row>
     <row r="50">
@@ -13882,16 +14250,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I50" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J50" t="n">
         <v>0.05558439708309018</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>0.4468728615062932</v>
       </c>
-      <c r="K50" t="n">
-        <v>0.03020996945621297</v>
-      </c>
       <c r="L50" t="n">
-        <v>0.07956960416033973</v>
+        <v>0.477136091816757</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.03821791338876894</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.07246915076786338</v>
       </c>
     </row>
     <row r="51">
@@ -13920,16 +14294,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I51" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J51" t="n">
         <v>0.0146175500591354</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>0.4468728615125712</v>
       </c>
-      <c r="K51" t="n">
-        <v>-0.007680457421789329</v>
-      </c>
       <c r="L51" t="n">
-        <v>0.03962027992870897</v>
+        <v>0.4771360918235034</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-0.00220209495708086</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.02909224258290118</v>
       </c>
     </row>
     <row r="52">
@@ -13958,16 +14338,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I52" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J52" t="n">
         <v>0.02201542226237296</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>0.4468728615149317</v>
       </c>
-      <c r="K52" t="n">
-        <v>-0.005678139529489744</v>
-      </c>
       <c r="L52" t="n">
-        <v>0.04353524564710372</v>
+        <v>0.47713609182604</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.005056557073351172</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.04051049703104988</v>
       </c>
     </row>
     <row r="53">
@@ -13996,16 +14382,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I53" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J53" t="n">
         <v>0.09899729193785185</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>0.4468728615158012</v>
       </c>
-      <c r="K53" t="n">
-        <v>0.05618809227756667</v>
-      </c>
       <c r="L53" t="n">
-        <v>0.1343348789456966</v>
+        <v>0.4771360918269744</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.06886940132937706</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.1321555775717554</v>
       </c>
     </row>
     <row r="54">
@@ -14034,16 +14426,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I54" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.01471965956873184</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>0.4468728615161149</v>
       </c>
-      <c r="K54" t="n">
-        <v>-0.005617407428258363</v>
-      </c>
       <c r="L54" t="n">
-        <v>0.03097633360321713</v>
+        <v>0.4771360918273115</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.00211840795871345</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.02752176562575946</v>
       </c>
     </row>
     <row r="55">
@@ -14072,16 +14470,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I55" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J55" t="n">
         <v>0.07153467848155119</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>0.4468728615162258</v>
       </c>
-      <c r="K55" t="n">
-        <v>0.04463646615236232</v>
-      </c>
       <c r="L55" t="n">
-        <v>0.09746139938514144</v>
+        <v>0.4771360918274307</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.051848324028013</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.09119322664521938</v>
       </c>
     </row>
     <row r="56">
@@ -14110,16 +14514,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I56" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J56" t="n">
         <v>-0.04435067922114632</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>0.4468728615162643</v>
       </c>
-      <c r="K56" t="n">
-        <v>-0.07146837294554836</v>
-      </c>
       <c r="L56" t="n">
-        <v>-0.01572419106915033</v>
+        <v>0.477136091827472</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-0.06581793382562566</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-0.02572910340296517</v>
       </c>
     </row>
     <row r="57">
@@ -14148,16 +14558,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I57" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J57" t="n">
         <v>0.06466803851248439</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>0.4468728615162773</v>
       </c>
-      <c r="K57" t="n">
-        <v>0.04187052327595402</v>
-      </c>
       <c r="L57" t="n">
-        <v>0.08671278900429841</v>
+        <v>0.477136091827486</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.04937768688350946</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.08175927648568869</v>
       </c>
     </row>
     <row r="58">
@@ -14186,16 +14602,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I58" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.0216804907924522</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>0.4468728615162816</v>
       </c>
-      <c r="K58" t="n">
-        <v>0.003119647063475662</v>
-      </c>
       <c r="L58" t="n">
-        <v>0.03802127581712932</v>
+        <v>0.4771360918274907</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.01161054149783137</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.03015284281603453</v>
       </c>
     </row>
     <row r="59">
@@ -14224,16 +14646,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I59" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J59" t="n">
         <v>-0.04876536729315869</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>0.446872861516283</v>
       </c>
-      <c r="K59" t="n">
-        <v>-0.06804619641823223</v>
-      </c>
       <c r="L59" t="n">
-        <v>-0.03020758642566912</v>
+        <v>0.4771360918274922</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-0.06489524015011813</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-0.03546836824954475</v>
       </c>
     </row>
     <row r="60">
@@ -14262,16 +14690,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I60" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J60" t="n">
         <v>0.02120921171857174</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>0.4468728615162835</v>
       </c>
-      <c r="K60" t="n">
-        <v>0.00295626247735519</v>
-      </c>
       <c r="L60" t="n">
-        <v>0.03853480656741031</v>
+        <v>0.4771360918274927</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.01075022568972875</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.02953754295104242</v>
       </c>
     </row>
     <row r="61">
@@ -14300,16 +14734,22 @@
         <v>0.01990264328443926</v>
       </c>
       <c r="I61" t="n">
+        <v>0.01084747669019326</v>
+      </c>
+      <c r="J61" t="n">
         <v>0.05092343265831147</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>0.4468728615162836</v>
       </c>
-      <c r="K61" t="n">
-        <v>0.02931381458983788</v>
-      </c>
       <c r="L61" t="n">
-        <v>0.07258319222287542</v>
+        <v>0.4771360918274928</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.03685111300163749</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.06392008160672695</v>
       </c>
     </row>
   </sheetData>
